--- a/docs/build_and_push_guide.xlsx
+++ b/docs/build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 22:04:17</t>
+          <t xml:space="preserve">2026-09-23 08:45:52</t>
         </is>
       </c>
     </row>
@@ -511,322 +511,317 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="49.5" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース → フロント → バックを続けてプッシュし、ベースのタグを受け渡したい</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">build_and_push_all.sh (各イメージ用ラッパー経由で本スクリプトを呼ぶ。5.9 参照)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《前提条件》</t>
         </is>
       </c>
-      <c r="B12" s="8"/>
-    </row>
-    <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="B13" s="8"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">前提</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">認証</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実行前に aws login --remote 済みであること。未認証なら exit 1</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限</t>
+          <t xml:space="preserve">認証</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR の操作権限。CodeCommit の権限は不要</t>
+          <t xml:space="preserve">実行前に aws login --remote 済みであること。未認証なら exit 1</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限が無い場合</t>
+          <t xml:space="preserve">権限</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定は警告して終了 (--warn-only)。--auto-switchback で自動スイッチバック</t>
+          <t xml:space="preserve">ECR の操作権限。CodeCommit の権限は不要</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">必須コマンド</t>
+          <t xml:space="preserve">権限が無い場合</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">docker、aws、docker compose または docker-compose</t>
+          <t xml:space="preserve">既定は警告して終了 (--warn-only)。--auto-switchback で自動スイッチバック</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">必須コマンド</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker、aws、docker compose または docker-compose</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Docker</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">デーモンに接続できること (起動時に docker info で確認)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《前提条件》</t>
         </is>
       </c>
-      <c r="B19" s="8"/>
-    </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B20" s="8"/>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B20" s="3"/>
-    </row>
-    <row r="21" ht="9.0" customHeight="1">
-      <c r="A21" s="0"/>
-    </row>
-    <row r="22" ht="24.0" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" ht="9.0" customHeight="1">
+      <c r="A22" s="0"/>
+    </row>
+    <row r="23" ht="24.0" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2. 全体構成</t>
         </is>
       </c>
-      <c r="B22" s="5"/>
-    </row>
-    <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.1 ファイル内のセクション構成》</t>
         </is>
       </c>
-      <c r="B23" s="8"/>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="B24" s="8"/>
+    </row>
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">行の位置</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">セクション</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="33.0" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+    <row r="26" ht="33.0" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">冒頭</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ヘッダーコメント</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">スクリプトの目的・前提・使い方</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="49.5" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="27" ht="49.5" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">表示タイムゾーン設定</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ・タグ・ログファイル名の時刻を JST に固定</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="33.0" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="28" ht="33.0" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">既定値</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全パラメータの初期値</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="49.5" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="29" ht="49.5" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前半</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ用ヘルパ</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">log / warn / err / diag / run / log_elapsed ほか</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">usage()</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--help の本文</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="49.5" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="31" ht="49.5" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数の事前走査</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--log-dir / --build-only を本パース前に解釈</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="33.0" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="32" ht="33.0" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログファイル出力の準備</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">tee によるコンソール出力の複製</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="49.5" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="33" ht="49.5" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--build-only 委譲</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh へ引数を引き継いで委譲</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="33.0" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="34" ht="33.0" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数パース</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">本パース (need_value で値欠落を検出)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="66.0" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="35" ht="66.0" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">中盤</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">各種検証</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss オプション排他 / 依存コマンド / Docker / AWS 認証 / イメージ参照</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="33.0" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ECR 権限チェック・スイッチバック</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">check_ecr_permission / do_switchback</t>
         </is>
       </c>
     </row>
@@ -838,29 +833,29 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">ECR 権限チェック・スイッチバック</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">check_ecr_permission / do_switchback</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="33.0" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">シークレット準備</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">prepare_jboss_password</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="49.5" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">後半</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一時ファイルコピー</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prepare_copy_files / cleanup_copied_files</t>
         </is>
       </c>
     </row>
@@ -872,271 +867,288 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">push 失敗診断</t>
+          <t xml:space="preserve">一時ファイルコピー</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">guide_iam ほか 5 種の原因ガイド + diagnose_push_failure</t>
+          <t xml:space="preserve">prepare_copy_files / cleanup_copied_files</t>
         </is>
       </c>
     </row>
     <row r="39" ht="49.5" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">後半</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">push 失敗診断</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guide_iam ほか 5 種の原因ガイド + diagnose_push_failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="49.5" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">末尾</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">メイン処理</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド → タグ付け → ログイン → プッシュ → 出力</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.2 主要な関数》</t>
         </is>
       </c>
-      <c r="B40" s="8"/>
-    </row>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="B41" s="8"/>
+    </row>
+    <row r="42" ht="19.5" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">関数</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">役割</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">setup_display_timezone</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asia/Tokyo → JST-9 の順に試し、表示時刻を JST に固定する</t>
         </is>
       </c>
     </row>
     <row r="43" ht="19.5" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">log / warn / err</t>
+          <t xml:space="preserve">setup_display_timezone</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[YYYY-MM-DD HH:MM:SS JST] 付きでログ出力 (warn/err は stderr)</t>
+          <t xml:space="preserve">Asia/Tokyo → JST-9 の順に試し、表示時刻を JST に固定する</t>
         </is>
       </c>
     </row>
     <row r="44" ht="19.5" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">diag</t>
+          <t xml:space="preserve">log / warn / err</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">診断ガイド用。接頭辞を付けずそのまま stderr へ出力</t>
+          <t xml:space="preserve">[YYYY-MM-DD HH:MM:SS JST] 付きでログ出力 (warn/err は stderr)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="19.5" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">run</t>
+          <t xml:space="preserve">diag</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--dry-run 時はコマンドを表示するだけ、通常時は実行する</t>
+          <t xml:space="preserve">診断ガイド用。接頭辞を付けずそのまま stderr へ出力</t>
         </is>
       </c>
     </row>
     <row r="46" ht="19.5" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">log_elapsed</t>
+          <t xml:space="preserve">run</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">開始からの経過秒数を HH:MM:SS 付きで出力 (EXIT トラップ)</t>
+          <t xml:space="preserve">--dry-run 時はコマンドを表示するだけ、通常時は実行する</t>
         </is>
       </c>
     </row>
     <row r="47" ht="19.5" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">log_elapsed</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">開始からの経過秒数を HH:MM:SS 付きで出力 (EXIT トラップ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">finish_logging</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ複製 (tee) を閉じて書き込み完了を待つ (ログ末尾の欠落防止)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="33.0" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="49" ht="33.0" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">new_temp_file / cleanup_temp_files</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">一時ファイルの安全な作成と一括削除</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">json_escape</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">imagedefinition.json に埋め込む値の JSON エスケープ</t>
         </is>
       </c>
     </row>
     <row r="50" ht="19.5" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">arg_takes_value / ecr_only_option</t>
+          <t xml:space="preserve">json_escape</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">事前走査で「値を取るオプション」「ECR 専用オプション」を判定</t>
+          <t xml:space="preserve">imagedefinition.json に埋め込む値の JSON エスケープ</t>
         </is>
       </c>
     </row>
     <row r="51" ht="19.5" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">need_value</t>
+          <t xml:space="preserve">arg_takes_value / ecr_only_option</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">値が必要なオプションで値が省略された場合にエラー終了</t>
+          <t xml:space="preserve">事前走査で「値を取るオプション」「ECR 専用オプション」を判定</t>
         </is>
       </c>
     </row>
     <row r="52" ht="19.5" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">check_ecr_permission</t>
+          <t xml:space="preserve">need_value</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws ecr get-login-password の可否で ECR 権限を判定。成功時はトークンを保持</t>
+          <t xml:space="preserve">値が必要なオプションで値が省略された場合にエラー終了</t>
         </is>
       </c>
     </row>
     <row r="53" ht="19.5" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">warn_ecr_auth_error</t>
+          <t xml:space="preserve">check_ecr_permission</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">上記が失敗したとき、AWS が返したエラー本文を表示</t>
+          <t xml:space="preserve">aws ecr get-login-password の可否で ECR 権限を判定。成功時はトークンを保持</t>
         </is>
       </c>
     </row>
     <row r="54" ht="19.5" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">do_switchback</t>
+          <t xml:space="preserve">warn_ecr_auth_error</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">別チーム提供のスイッチバック用シェルを source で読み込む</t>
+          <t xml:space="preserve">上記が失敗したとき、AWS が返したエラー本文を表示</t>
         </is>
       </c>
     </row>
     <row r="55" ht="19.5" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">do_switchback</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">別チーム提供のスイッチバック用シェルを source で読み込む</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">prepare_jboss_password</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストア等からマスターパスワードを取得し環境変数へ export</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="33.0" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="57" ht="33.0" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">prepare_copy_files / cleanup_copied_files</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド前の一時コピーと、終了時の自動削除</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="58" ht="19.5" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">diagnose_push_failure</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">push 失敗時に AWS API を実際に叩いて原因を切り分け、調査手順を表示</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ》</t>
         </is>
       </c>
-      <c r="B58" s="8"/>
-    </row>
-    <row r="59" ht="33.0" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="B59" s="8"/>
+    </row>
+    <row r="60" ht="33.0" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">処理のどの経路 (成功・失敗・中断) でも、以下が必ず実行されます。
 SIGINT (Ctrl-C) / SIGTERM で中断した場合も EXIT トラップが動作します。</t>
         </is>
       </c>
-      <c r="B59" s="3"/>
-    </row>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="B60" s="3"/>
+    </row>
+    <row r="61" ht="19.5" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ》</t>
         </is>
       </c>
-      <c r="B60" s="8"/>
-    </row>
-    <row r="61" ht="66.0" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="B61" s="8"/>
+    </row>
+    <row r="62" ht="66.0" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">cleanup_copied_files   … --copy-file でコピーしたファイルを削除
 cleanup_temp_files     … 一時ファイル (push ログ・SSM エラー出力) を削除
@@ -1144,263 +1156,241 @@
 finish_logging         … ログファイルへの書き込みを完了させる</t>
         </is>
       </c>
-      <c r="B61" s="6"/>
-    </row>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="B62" s="6"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《2.3 EXIT トラップ》</t>
         </is>
       </c>
-      <c r="B62" s="8"/>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="B63" s="8"/>
+    </row>
+    <row r="64" ht="19.5" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B63" s="3"/>
-    </row>
-    <row r="64" ht="9.0" customHeight="1">
-      <c r="A64" s="0"/>
-    </row>
-    <row r="65" ht="24.0" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="B64" s="3"/>
+    </row>
+    <row r="65" ht="9.0" customHeight="1">
+      <c r="A65" s="0"/>
+    </row>
+    <row r="66" ht="24.0" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">3. 処理の流れ</t>
         </is>
       </c>
-      <c r="B65" s="5"/>
-    </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.1 全体フロー》</t>
-        </is>
-      </c>
-      <c r="B66" s="8"/>
+      <c r="B66" s="5"/>
     </row>
     <row r="67" ht="19.5" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">《3.1 全体フロー》</t>
+        </is>
+      </c>
+      <c r="B67" s="8"/>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">《3.2 各ステップの詳細》</t>
         </is>
       </c>
-      <c r="B67" s="8"/>
-    </row>
-    <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="B68" s="8"/>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">#</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ステップ</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">失敗時</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="99.0" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">タイムゾーン設定</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asia/Tokyo が使えなければ tzdata 不要の JST-9 へフォールバック。どちらも不可ならホストの TZ で継続 (警告)</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">警告のみ</t>
         </is>
       </c>
     </row>
     <row r="70" ht="99.0" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">タイムゾーン設定</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia/Tokyo が使えなければ tzdata 不要の JST-9 へフォールバック。どちらも不可ならホストの TZ で継続 (警告)</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">警告のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="99.0" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数の事前走査</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--log-dir の値取得と --build-only の検出。「値を取るオプションの値」をオプション名と取り違えないよう走査する</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="82.5" customHeight="1">
-      <c r="A71" s="11" t="inlineStr">
+    <row r="72" ht="82.5" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ログ複製開始</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--log-dir 指定時、DIR/build_and_push_&lt;YYYYMMDDHHMMSS&gt;.log へ全出力を複製 (画面表示は継続)</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ディレクトリ作成失敗で exit 1</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="99.0" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
+    <row r="73" ht="99.0" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--build-only 委譲</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">build_and_verify.sh を起動。ECR 専用オプションは警告して除去、--log-dir は委譲元で処理済みのため除去</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">委譲先が無ければ exit 1</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="49.5" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
+    <row r="74" ht="49.5" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数パース</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">全オプションを解釈。値が必要なのに省略された場合は exit 2</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exit 2</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="82.5" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
+    <row r="75" ht="82.5" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">JBoss オプション検証</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--jboss-password-param と --jboss-password の同時指定禁止、環境変数名の形式検証</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exit 2</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="33.0" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
+    <row r="76" ht="33.0" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">必須コマンド確認</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">docker と aws の存在確認</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exit 1</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="66.0" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
+    <row r="77" ht="66.0" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Docker 接続確認</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">docker info でデーモンへ接続できるか確認 (--dry-run 時は警告のみ)</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exit 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="49.5" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS 認証確認</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aws sts get-caller-identity (--dry-run 時は警告のみ)</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -1412,61 +1402,61 @@
     <row r="78" ht="49.5" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AWS 認証確認</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aws sts get-caller-identity (--dry-run 時は警告のみ)</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="49.5" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose 判定</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">docker compose (v2) を優先、無ければ docker-compose (v1)</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exit 1</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="115.5" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
+    <row r="80" ht="115.5" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">レジストリ URL</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--registry 指定時はそれを使用。未指定なら &lt;account-id&gt;.dkr.ecr.&lt;region&gt;.amazonaws.com を組み立て。末尾のスラッシュは除去</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exit 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="82.5" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">イメージ参照の検証</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--repository は小文字のみ、--tag-prefix は英数字と . _ - のみ。ビルド前に検証する</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -1478,527 +1468,566 @@
     <row r="81" ht="82.5" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR 権限チェック</t>
+          <t xml:space="preserve">イメージ参照の検証</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws ecr get-login-password の成否で判定。成功時のトークンは後段の docker login に再利用</t>
+          <t xml:space="preserve">--repository は小文字のみ、--tag-prefix は英数字と . _ - のみ。ビルド前に検証する</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">下記 3.3 参照</t>
+          <t xml:space="preserve">exit 2</t>
         </is>
       </c>
     </row>
     <row r="82" ht="82.5" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECR 権限チェック</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aws ecr get-login-password の成否で判定。成功時のトークンは後段の docker login に再利用</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">下記 3.3 参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="82.5" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">シークレット準備</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">パラメータストア / 直接指定 / 既存環境変数のいずれかからマスターパスワードを取得し export</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exit 1</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="66.0" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="84" ht="66.0" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">事前コピー</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--copy-file SRC:DEST_DIR を検証してコピー。終了時に自動削除</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exit 1 / exit 2</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="148.5" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
+    <row r="85" ht="214.5" customHeight="1">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">docker compose -f &lt;file&gt; build [--no-cache] [service] を監視プロセス付きで実行 (進捗表示・停滞検知・上限時間での中断。5.7 参照)。開始前に data root の空き容量を確認</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker compose -f &lt;file&gt; build [--no-cache] [--build-arg BASE_IMAGE_TAG=&lt;tag&gt;] [service] を監視プロセス付きで実行 (--build-arg は --base-image-tag 指定時のみ) (進捗表示・停滞検知・上限時間での中断。5.7 参照)。開始前に data root の空き容量を確認</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exit 1</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="66.0" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
+    <row r="86" ht="66.0" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">イメージ確認</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">docker image inspect &lt;local-image&gt; (--dry-run 時はスキップ)</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exit 1</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="33.0" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
+    <row r="87" ht="33.0" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">タグ生成</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;TAG_PREFIX&gt;-&lt;YYYYMMDDHHMMSS&gt; (JST)</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="66.0" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ECR ログイン</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">docker login --username AWS --password-stdin (パスワードは標準入力経由)</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exit 1</t>
         </is>
       </c>
     </row>
     <row r="88" ht="66.0" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECR ログイン</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker login --username AWS --password-stdin (パスワードは標準入力経由)</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="66.0" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">タグ付け・プッシュ</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">docker image tag → docker push。出力は tee で保存し、失敗時に解析</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exit 1 + 診断</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="49.5" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
+    <row r="90" ht="115.5" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">21</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">出力</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">imagedefinition.json を書き込み (書き込み失敗も検出)</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition.json を書き込み (書き込み失敗も検出)。--image-uri-file 指定時は、最後にプッシュしたイメージの参照を書き出す</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">exit 1</t>
         </is>
       </c>
-    </row>
-    <row r="90" ht="19.5" customHeight="1">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《3.3 ECR 権限チェックの分岐》</t>
-        </is>
-      </c>
-      <c r="B90" s="8"/>
     </row>
     <row r="91" ht="19.5" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">《3.3 ECR 権限チェックの分岐》</t>
+        </is>
+      </c>
+      <c r="B91" s="8"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">《3.4 push 失敗時の自動診断》</t>
         </is>
       </c>
-      <c r="B91" s="8"/>
-    </row>
-    <row r="92" ht="33.0" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="B92" s="8"/>
+    </row>
+    <row r="93" ht="33.0" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">docker push が失敗すると、出力内容と AWS API の応答から原因を推定し、
 該当する原因カテゴリの「詳細説明 + AWS CLI 調査コマンド + AWS コンソール確認箇所」を表示します。</t>
         </is>
       </c>
-      <c r="B92" s="3"/>
-    </row>
-    <row r="93" ht="19.5" customHeight="1">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="B93" s="3"/>
+    </row>
+    <row r="94" ht="19.5" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 push 失敗時の自動診断》</t>
         </is>
       </c>
-      <c r="B93" s="8"/>
-    </row>
-    <row r="94" ht="19.5" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="B94" s="8"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">カテゴリ</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">検出キーワード例</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">主な調査項目</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="66.0" customHeight="1">
-      <c r="A95" s="11" t="inlineStr">
+    <row r="96" ht="66.0" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">A. IAM 権限エラー</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">not authorized to perform、denied:</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">sts get-caller-identity、simulate-principal-policy、CloudTrail</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="49.5" customHeight="1">
-      <c r="A96" s="11" t="inlineStr">
+    <row r="97" ht="49.5" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">B. エンドポイント権限設定</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同上 (A と併記)</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">リポジトリポリシー、VPC エンドポイントポリシー</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="66.0" customHeight="1">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C. エンドポイント不存在</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no such host、dial tcp、i/o timeout</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ecr.api / ecr.dkr / s3 エンドポイント、PrivateDNS、SG、ルートテーブル</t>
         </is>
       </c>
     </row>
     <row r="98" ht="66.0" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">C. エンドポイント不存在</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no such host、dial tcp、i/o timeout</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecr.api / ecr.dkr / s3 エンドポイント、PrivateDNS、SG、ルートテーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="66.0" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">D. リポジトリ不存在</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">name unknown、does not exist</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">describe-repositories、リージョン取り違え、create-repository</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="19.5" customHeight="1">
-      <c r="A99" s="11" t="inlineStr">
+    <row r="100" ht="19.5" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">E. トークン期限切れ</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">authorization token has expired、401 Unauthorized</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">再ログイン手順</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="19.5" customHeight="1">
-      <c r="A100" s="8" t="inlineStr">
+    <row r="101" ht="19.5" customHeight="1">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 push 失敗時の自動診断》</t>
         </is>
       </c>
-      <c r="B100" s="8"/>
-    </row>
-    <row r="101" ht="49.5" customHeight="1">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="B101" s="8"/>
+    </row>
+    <row r="102" ht="49.5" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">診断では、実際に aws sts get-caller-identity と aws ecr describe-repositories を
 読み取り専用で呼び出し、事実確認した結果も併せて表示します。
 どのパターンにも一致しない場合は、A〜E の全観点を表示します。</t>
         </is>
       </c>
-      <c r="B101" s="3"/>
-    </row>
-    <row r="102" ht="19.5" customHeight="1">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="B102" s="3"/>
+    </row>
+    <row r="103" ht="19.5" customHeight="1">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《3.4 push 失敗時の自動診断》</t>
         </is>
       </c>
-      <c r="B102" s="8"/>
-    </row>
-    <row r="103" ht="19.5" customHeight="1">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="B103" s="8"/>
+    </row>
+    <row r="104" ht="19.5" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B103" s="3"/>
-    </row>
-    <row r="104" ht="9.0" customHeight="1">
-      <c r="A104" s="0"/>
-    </row>
-    <row r="105" ht="24.0" customHeight="1">
-      <c r="A105" s="5" t="inlineStr">
+      <c r="B104" s="3"/>
+    </row>
+    <row r="105" ht="9.0" customHeight="1">
+      <c r="A105" s="0"/>
+    </row>
+    <row r="106" ht="24.0" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">4. 入出力ファイル</t>
         </is>
       </c>
-      <c r="B105" s="5"/>
-    </row>
-    <row r="106" ht="19.5" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="B106" s="5"/>
+    </row>
+    <row r="107" ht="19.5" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">種別</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ファイル</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="49.5" customHeight="1">
-      <c r="A107" s="11" t="inlineStr">
+    <row r="108" ht="49.5" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">入力</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose.yml (--compose-file)</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルド定義。image: j1/base.local を含む</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="33.0" customHeight="1">
-      <c r="A108" s="11" t="inlineStr">
+    <row r="109" ht="33.0" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">入力</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Dockerfile</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">compose から参照される</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="19.5" customHeight="1">
-      <c r="A109" s="11" t="inlineStr">
+    <row r="110" ht="19.5" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">入力</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--switchback-shell のパス</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">source で読み込む</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="49.5" customHeight="1">
-      <c r="A110" s="11" t="inlineStr">
+    <row r="111" ht="49.5" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">出力</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">imagedefinition.json (--output)</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CodePipeline 用。name と imageUri を含む</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="19.5" customHeight="1">
-      <c r="A111" s="11" t="inlineStr">
+    <row r="112" ht="99.0" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">出力</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--log-dir 配下のログ</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画面出力の複製</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="19.5" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一時</t>
-        </is>
-      </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コピーしたファイル</t>
+          <t xml:space="preserve">--image-uri-file のパス</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">終了時に自動削除</t>
+          <t xml:space="preserve">プッシュしたイメージの参照を 1 行で記録 (呼び出し元への受け渡し用)。--dry-run 時もプレビュー上の参照を書き出す</t>
         </is>
       </c>
     </row>
     <row r="113" ht="19.5" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">出力</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--log-dir 配下のログ</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画面出力の複製</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="19.5" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">一時</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コピーしたファイル</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了時に自動削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="19.5" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一時</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">push ログ・SSM エラー出力</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C115" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">終了時に自動削除</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="19.5" customHeight="1">
-      <c r="A114" s="3" t="inlineStr">
+    <row r="116" ht="19.5" customHeight="1">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">imagedefinition.json の内容:</t>
         </is>
       </c>
-      <c r="B114" s="3"/>
-    </row>
-    <row r="115" ht="99.0" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
+      <c r="B116" s="3"/>
+    </row>
+    <row r="117" ht="99.0" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">[
   {
@@ -2008,377 +2037,377 @@
 ]</t>
         </is>
       </c>
-      <c r="B115" s="6"/>
-    </row>
-    <row r="116" ht="19.5" customHeight="1">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="B117" s="6"/>
+    </row>
+    <row r="118" ht="19.5" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B116" s="3"/>
-    </row>
-    <row r="117" ht="9.0" customHeight="1">
-      <c r="A117" s="0"/>
-    </row>
-    <row r="118" ht="24.0" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="B118" s="3"/>
+    </row>
+    <row r="119" ht="9.0" customHeight="1">
+      <c r="A119" s="0"/>
+    </row>
+    <row r="120" ht="24.0" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">5. 終了コード</t>
         </is>
       </c>
-      <c r="B118" s="5"/>
-    </row>
-    <row r="119" ht="19.5" customHeight="1">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="B120" s="5"/>
+    </row>
+    <row r="121" ht="19.5" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">コード</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">意味</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">主な発生条件</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="66.0" customHeight="1">
-      <c r="A120" s="11" t="inlineStr">
+    <row r="122" ht="66.0" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">正常終了</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">プッシュと imagedefinition 出力が完了 / --help / --dry-run 完走</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="247.5" customHeight="1">
-      <c r="A121" s="11" t="inlineStr">
+    <row r="123" ht="247.5" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">実行時エラー</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS 未認証、Docker デーモン未接続、ECR 権限なし、スイッチバック失敗、SSM 取得失敗、コピー失敗、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、ログイン失敗、タグ付け失敗、push 失敗、出力書き込み失敗、ログディレクトリ作成失敗、必須コマンド不足</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="165.0" customHeight="1">
-      <c r="A122" s="11" t="inlineStr">
+    <row r="124" ht="247.5" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">引数エラー</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、ビルド監視の各値が 0 未満か非数値、--account-id/--registry 未指定、リポジトリ名・タグ接頭辞の形式違反、JBoss オプションの排他違反、--copy-file の書式不正</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="19.5" customHeight="1">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不明なオプション、値の欠落、ビルド監視の各値が 0 未満か非数値、--account-id/--registry 未指定、リポジトリ名・タグ接頭辞・--base-image-tag の形式違反、--image-uri-file の出力先ディレクトリ不在 (またはディレクトリを指定)、JBoss オプションの排他違反、--copy-file の書式不正</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="19.5" customHeight="1">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--build-only 委譲時は、委譲先 build_and_verify.sh の終了コードがそのまま返ります。</t>
         </is>
       </c>
-      <c r="B123" s="3"/>
-    </row>
-    <row r="124" ht="19.5" customHeight="1">
-      <c r="A124" s="3" t="inlineStr">
+      <c r="B125" s="3"/>
+    </row>
+    <row r="126" ht="19.5" customHeight="1">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B124" s="3"/>
-    </row>
-    <row r="125" ht="9.0" customHeight="1">
-      <c r="A125" s="0"/>
-    </row>
-    <row r="126" ht="24.0" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+      <c r="B126" s="3"/>
+    </row>
+    <row r="127" ht="9.0" customHeight="1">
+      <c r="A127" s="0"/>
+    </row>
+    <row r="128" ht="24.0" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">6. 環境変数</t>
         </is>
       </c>
-      <c r="B126" s="5"/>
-    </row>
-    <row r="127" ht="19.5" customHeight="1">
-      <c r="A127" s="8" t="inlineStr">
+      <c r="B128" s="5"/>
+    </row>
+    <row r="129" ht="19.5" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《6.1 入力として参照する環境変数》</t>
         </is>
       </c>
-      <c r="B127" s="8"/>
-    </row>
-    <row r="128" ht="19.5" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="B129" s="8"/>
+    </row>
+    <row r="130" ht="19.5" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">対応オプション</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="33.0" customHeight="1">
-      <c r="A129" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_ACCOUNT_ID</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--account-id</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">レジストリ URL の組み立てに使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="33.0" customHeight="1">
-      <c r="A130" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--region</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">未指定時は ap-northeast-1</t>
         </is>
       </c>
     </row>
     <row r="131" ht="33.0" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR_REGISTRY</t>
+          <t xml:space="preserve">AWS_ACCOUNT_ID</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--registry</t>
+          <t xml:space="preserve">--account-id</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">レジストリ URL の直接指定</t>
+          <t xml:space="preserve">レジストリ URL の組み立てに使用</t>
         </is>
       </c>
     </row>
     <row r="132" ht="33.0" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWITCHBACK_SHELL</t>
+          <t xml:space="preserve">AWS_REGION → AWS_DEFAULT_REGION</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--switchback-shell</t>
+          <t xml:space="preserve">--region</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">スイッチバック用シェルのパス</t>
+          <t xml:space="preserve">未指定時は ap-northeast-1</t>
         </is>
       </c>
     </row>
     <row r="133" ht="33.0" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">ECR_REGISTRY</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--registry</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">レジストリ URL の直接指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="33.0" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWITCHBACK_SHELL</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--switchback-shell</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スイッチバック用シェルのパス</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="33.0" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名)</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--jboss-password-env</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">事前 export した値をそのまま使用</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="66.0" customHeight="1">
-      <c r="A134" s="11" t="inlineStr">
+    <row r="136" ht="66.0" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名)</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">--cacert-bundle-env</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">事前 export 済みなら、その tar のパスをそのまま使用 (--cacert-dir 未指定時)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="82.5" customHeight="1">
-      <c r="A135" s="11" t="inlineStr">
+    <row r="137" ht="82.5" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">BUILDKIT_PROGRESS</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ビルドログの表示形式。未指定時は plain を使用。ビルド監視が有効な間は tty を plain へ切り替える</t>
         </is>
       </c>
-    </row>
-    <row r="136" ht="19.5" customHeight="1">
-      <c r="A136" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">《6.1 入力として参照する環境変数》</t>
-        </is>
-      </c>
-      <c r="B136" s="8"/>
-    </row>
-    <row r="137" ht="19.5" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">オプションで指定した値が環境変数より優先されます。</t>
-        </is>
-      </c>
-      <c r="B137" s="3"/>
     </row>
     <row r="138" ht="19.5" customHeight="1">
       <c r="A138" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">《6.1 入力として参照する環境変数》</t>
+        </is>
+      </c>
+      <c r="B138" s="8"/>
+    </row>
+    <row r="139" ht="19.5" customHeight="1">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">オプションで指定した値が環境変数より優先されます。</t>
+        </is>
+      </c>
+      <c r="B139" s="3"/>
+    </row>
+    <row r="140" ht="19.5" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">《6.2 スクリプトが設定する環境変数》</t>
         </is>
       </c>
-      <c r="B138" s="8"/>
-    </row>
-    <row r="139" ht="19.5" customHeight="1">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="B140" s="8"/>
+    </row>
+    <row r="141" ht="19.5" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">環境変数</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">用途</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="19.5" customHeight="1">
-      <c r="A140" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TZ</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asia/Tokyo または JST-9 に設定し、表示時刻を JST に統一</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="33.0" customHeight="1">
-      <c r="A141" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぎ、ビルド監視が行単位で読めるようにする</t>
         </is>
       </c>
     </row>
     <row r="142" ht="19.5" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">TZ</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia/Tokyo または JST-9 に設定し、表示時刻を JST に統一</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="33.0" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定 plain。tty の上書き表示でビルドログが欠落するのを防ぎ、ビルド監視が行単位で読めるようにする</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="19.5" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">&lt;--jboss-password-env の値&gt;</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr">
+      <c r="B144" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">BuildKit シークレットとして compose へ渡す</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="19.5" customHeight="1">
-      <c r="A143" s="11" t="inlineStr">
+    <row r="145" ht="19.5" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
-      <c r="B143" s="3" t="inlineStr">
+      <c r="B145" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">同梱 compose.yml 用に必ず定義 (未使用時は空文字)</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="33.0" customHeight="1">
-      <c r="A144" s="11" t="inlineStr">
+    <row r="146" ht="33.0" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;--cacert-bundle-env の値&gt;</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="B146" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CA 証明書をまとめた tar のパス。compose の file 型シークレットへ渡す。--cacert-dir 未指定時は「空の tar」のパスが入り、従来どおり証明書なしでビルドされる</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="19.5" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
+    <row r="147" ht="19.5" customHeight="1">
+      <c r="A147" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">《6.2 スクリプトが設定する環境変数》</t>
         </is>
       </c>
-      <c r="B145" s="8"/>
-    </row>
-    <row r="146" ht="19.5" customHeight="1">
-      <c r="A146" s="3" t="inlineStr">
+      <c r="B147" s="8"/>
+    </row>
+    <row r="148" ht="19.5" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">---</t>
         </is>
       </c>
-      <c r="B146" s="3"/>
+      <c r="B148" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="43">
@@ -2388,43 +2417,43 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A41:B41"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A94:B94"/>
     <mergeCell ref="A101:B101"/>
     <mergeCell ref="A102:B102"/>
     <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="A106:B106"/>
     <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A117:B117"/>
     <mergeCell ref="A118:B118"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="A125:B125"/>
     <mergeCell ref="A126:B126"/>
-    <mergeCell ref="A127:B127"/>
-    <mergeCell ref="A136:B136"/>
-    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="A129:B129"/>
     <mergeCell ref="A138:B138"/>
-    <mergeCell ref="A145:B145"/>
-    <mergeCell ref="A146:B146"/>
+    <mergeCell ref="A139:B139"/>
+    <mergeCell ref="A140:B140"/>
+    <mergeCell ref="A147:B147"/>
+    <mergeCell ref="A148:B148"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2789,7 +2818,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="33.0" customHeight="1">
+    <row r="14" ht="66.0" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 ビルドと出力</t>
@@ -2797,17 +2826,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-progress-interval SEC</t>
+          <t xml:space="preserve">--base-image-tag TAG</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 以上の整数 (秒)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">英数字と . _ - (先頭は英数字か _、128 文字以内)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし = 渡さない)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -2817,7 +2846,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない (5.7 参照)</t>
+          <t xml:space="preserve">指定した場合のみ、ビルド引数 BASE_IMAGE_TAG=TAG として compose build へ渡す (--build-arg)。フロント / バックのように、プッシュ済みのベースイメージを FROM で参照するイメージのビルドで使う。ベースイメージ自体のビルドでは指定しない (5.9 参照)</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2858,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-stall-timeout SEC</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2839,7 +2868,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">300</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -2849,7 +2878,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない (5.7 参照)</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2890,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-timeout SEC</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2871,7 +2900,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (無制限)</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -2881,7 +2910,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
@@ -2893,147 +2922,155 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--build-timeout SEC</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (無制限)</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="33.0" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--no-build-watchdog</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">フラグ</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">上記の監視をすべて行わない。監視が有効な間は BUILDKIT_PROGRESS=tty を plain へ切り替えるため、tty 形式を使いたい場合に指定する</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 ビルドと出力</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--container-name NAME</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">任意の文字列</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">--repository の値</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">imagedefinition.json の name</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="33.0" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="20" ht="33.0" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 ビルドと出力</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--output FILE</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">imagedefinition.json</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">不可</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">imagedefinition の出力先</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.3 実行制御・ログ</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--dry-run</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ビルド/ログイン/タグ付け/プッシュ/ファイル出力を行わず、実行内容のみ表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
+    <row r="21" ht="66.0" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 実行制御・ログ</t>
+          <t xml:space="preserve">4.2 ビルドと出力</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--build-only</t>
+          <t xml:space="preserve">--image-uri-file FILE</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">ファイルパス</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="E21" s="7"/>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルドのみ実行 (build_and_verify.sh へ委譲)。ECR 関連処理は行わない</t>
+          <t xml:space="preserve">プッシュしたイメージの参照 (&lt;registry&gt;/&lt;repository&gt;:&lt;tag&gt;) を 1 行で書き出す。呼び出し元のスクリプト (build_and_push_all.sh など) がタグを受け取るためのもの。プッシュと imagedefinition の出力が済んだ最後に書き出す。--dry-run 時もプレビュー上の参照を書き出す (5.9 参照)</t>
         </is>
       </c>
     </row>
@@ -3045,23 +3082,23 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--log-dir DIR</t>
+          <t xml:space="preserve">--dry-run</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力を DIR/build_and_push_&lt;日時&gt;.log にも保存。ディレクトリは自動作成</t>
+          <t xml:space="preserve">ビルド/ログイン/タグ付け/プッシュ/ファイル出力を行わず、実行内容のみ表示</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3110,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
+          <t xml:space="preserve">--build-only</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -3083,30 +3120,30 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルドのみ実行 (build_and_verify.sh へ委譲)。ECR 関連処理は行わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 ビルド前後の一時ファイル</t>
+          <t xml:space="preserve">4.3 実行制御・ログ</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
+          <t xml:space="preserve">--log-dir DIR</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3114,59 +3151,55 @@
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+      <c r="E24" s="7"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前にコピーし、終了後 (成功・失敗を問わず) 自動削除</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="49.5" customHeight="1">
+          <t xml:space="preserve">画面出力を DIR/build_and_push_&lt;日時&gt;.log にも保存。ディレクトリは自動作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.3 実行制御・ログ</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-param NAME</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SSM パラメータ名</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストアから取得 (--with-decryption)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="49.5" customHeight="1">
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="33.0" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.4 ビルド前後の一時ファイル</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password VALUE</t>
+          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パスワード文字列</t>
+          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -3174,10 +3207,14 @@
           <t xml:space="preserve">(なし)</t>
         </is>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+          <t xml:space="preserve">ビルド前にコピーし、終了後 (成功・失敗を問わず) 自動削除</t>
         </is>
       </c>
     </row>
@@ -3189,83 +3226,83 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">--jboss-password-param NAME</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">SSM パラメータ名</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="33.0" customHeight="1">
+          <t xml:space="preserve">パラメータストアから取得 (--with-decryption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="49.5" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 スイッチバック</t>
+          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--switchback-shell PATH</t>
+          <t xml:space="preserve">--jboss-password VALUE</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シェルスクリプトのパス</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
+          <t xml:space="preserve">パスワード文字列</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">別チーム提供のスイッチバック用シェル (source で読み込む)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
+          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="49.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.6 スイッチバック</t>
+          <t xml:space="preserve">4.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--auto-switchback</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR 権限が無い場合に自動でスイッチバックして継続</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
+          <t xml:space="preserve">受け渡しに使う環境変数名。単独指定時は既存の環境変数値を使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="33.0" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6 スイッチバック</t>
@@ -3273,83 +3310,79 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--warn-only</t>
+          <t xml:space="preserve">--switchback-shell PATH</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">シェルスクリプトのパス</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定</t>
+          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
         </is>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR 権限が無い場合に警告して終了</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="33.0" customHeight="1">
+          <t xml:space="preserve">別チーム提供のスイッチバック用シェル (source で読み込む)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.6 スイッチバック</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-dir DIR</t>
+          <t xml:space="preserve">--auto-switchback</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリのパス</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E31" s="7"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ECR 権限が無い場合に自動でスイッチバックして継続</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+          <t xml:space="preserve">4.6 スイッチバック</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-secret-id ID</t>
+          <t xml:space="preserve">--warn-only</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">英数字と . _ -</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cacerts</t>
+          <t xml:space="preserve">既定</t>
         </is>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シークレット id。compose.yml の secrets 名、Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">ECR 権限が無い場合に警告して終了</t>
         </is>
       </c>
     </row>
@@ -3361,23 +3394,27 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle PATH</t>
+          <t xml:space="preserve">--cacert-dir DIR</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパス</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一時ファイル</t>
-        </is>
-      </c>
-      <c r="E33" s="7"/>
+          <t xml:space="preserve">ディレクトリのパス</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめてビルドへ渡す</t>
         </is>
       </c>
     </row>
@@ -3389,23 +3426,23 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
+          <t xml:space="preserve">英数字と . _ -</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+          <t xml:space="preserve">cacerts</t>
         </is>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
+          <t xml:space="preserve">シークレット id。compose.yml の secrets 名、Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
         </is>
       </c>
     </row>
@@ -3417,32 +3454,88 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tar のパス</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一時ファイル</t>
+        </is>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="33.0" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle-env NAME</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境変数名</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE</t>
+        </is>
+      </c>
+      <c r="E36" s="7"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tar のパスを compose へ渡す環境変数名。compose.yml の file: が参照する変数名と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="33.0" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">--cacert-glob PATTERN</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">glob パターン</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">*.crt と *.pem</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">可</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F35"/>
+  <autoFilter ref="A4:F37"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -4028,12 +4121,12 @@
     <row r="32" ht="33.0" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">build_and_push_all.sh の引数と終了コード</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env / 事前 export した値をそのまま使用</t>
+          <t xml:space="preserve">--base-script PATH / ベースイメージ用ラッパー (既定: &lt;スクリプトの場所&gt;/build_and_push_base.sh)</t>
         </is>
       </c>
       <c r="C32" s="3"/>
@@ -4042,12 +4135,12 @@
     <row r="33" ht="33.0" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">build_and_push_all.sh の引数と終了コード</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-bundle-env / 事前 export 済みなら、その tar のパスをそのまま使用 (--cacert-dir 未指定時)</t>
+          <t xml:space="preserve">--front-script PATH / フロントイメージ用ラッパー (既定: &lt;スクリプトの場所&gt;/build_and_push_front.sh)</t>
         </is>
       </c>
       <c r="C33" s="3"/>
@@ -4056,19 +4149,61 @@
     <row r="34" ht="33.0" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2 スクリプトが設定する環境変数</t>
+          <t xml:space="preserve">build_and_push_all.sh の引数と終了コード</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぎ、ビルド監視が行単位で読めるようにする</t>
+          <t xml:space="preserve">--back-script PATH / バックイメージ用ラッパー (既定: &lt;スクリプトの場所&gt;/build_and_push_back.sh)</t>
         </is>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
+    <row r="35" ht="33.0" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env / 事前 export した値をそのまま使用</t>
+        </is>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" ht="33.0" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CACERT_BUNDLE_FILE (既定名) / --cacert-bundle-env / 事前 export 済みなら、その tar のパスをそのまま使用 (--cacert-dir 未指定時)</t>
+        </is>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+    </row>
+    <row r="37" ht="33.0" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2 スクリプトが設定する環境変数</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUILDKIT_PROGRESS / 既定 plain。tty の上書き表示でビルドログが欠落するのを防ぎ、ビルド監視が行単位で読めるようにする</t>
+        </is>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -4080,6 +4215,9 @@
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4292,7 +4430,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="82.5" customHeight="1">
+    <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
@@ -4300,14 +4438,51 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">レジストリを直接指定 (アカウント ID 不要)
+          <t xml:space="preserve">レジストリを直接指定 (アカウント ID 不要)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_push.sh --registry 123456789012.dkr.ecr.ap-northeast-1.amazonaws.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66.0" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フロントイメージ: プッシュ済みベースイメージのタグをビルド引数 BASE_IMAGE_TAG で渡す</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_push.sh --account-id 123456789012 \
+    --repository frontimage --tag-prefix FrontImage \
+    --compose-service frontend --local-image j1/front.local \
+    --base-image-tag BaseImage-20260923120000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="99.0" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース → フロント → バックをラッパー経由で一括実行し、タグを受け渡す (5.9 参照)
 ビルドが exporting layers から進まないときの調査 (進捗 10 秒 / 停滞判定 60 秒)
 30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">./build_and_push.sh --registry 123456789012.dkr.ecr.ap-northeast-1.amazonaws.com
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">./build_and_push_all.sh
 ./build_and_push.sh --account-id 123456789012 \
     --build-progress-interval 10 --build-stall-timeout 60
 ./build_and_push.sh --account-id 123456789012 --build-timeout 1800</t>
